--- a/data/trans_orig/P79A1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A1_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>929</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>53565</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
